--- a/clean_output.xlsx
+++ b/clean_output.xlsx
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ruth Kyomuhendo</t>
+          <t>Ruth Evace Kyomuhendo</t>
         </is>
       </c>
     </row>
